--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_review_display.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_review_display.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="3">
@@ -465,36 +465,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C3" t="n">
-        <v>36.5</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Ratings Bar Only (Visual breakdown of star ratings)</t>
+          <t>Summary Only (Average rating and total count)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Summary Only (Average rating and total count)</t>
+          <t>Ratings Bar Only (Visual breakdown of star ratings)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>11.5</v>
+        <v>12.05</v>
       </c>
     </row>
   </sheetData>
